--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130229034</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>130229175</v>
       </c>
       <c r="B4" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130229034</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>130229175</v>
       </c>
       <c r="B4" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130229034</v>
       </c>
       <c r="B2" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97544</v>
+        <v>97570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>130229175</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130229034</v>
       </c>
       <c r="B2" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97570</v>
+        <v>97571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>130229175</v>
       </c>
       <c r="B4" t="n">
-        <v>91530</v>
+        <v>91531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130229034</v>
       </c>
       <c r="B2" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97571</v>
+        <v>97572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>130229175</v>
       </c>
       <c r="B4" t="n">
-        <v>91531</v>
+        <v>91532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130229034</v>
       </c>
       <c r="B2" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97572</v>
+        <v>97574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>130229175</v>
       </c>
       <c r="B4" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130229034</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97574</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130229034</v>
+        <v>130229403</v>
       </c>
       <c r="B2" t="n">
-        <v>97828</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>282970</v>
+        <v>282929</v>
       </c>
       <c r="R2" t="n">
-        <v>6528781</v>
+        <v>6528795</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +771,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>barcode</t>
+          <t>mikroskoperad</t>
         </is>
       </c>
       <c r="AG2" t="b">
@@ -804,7 +795,7 @@
         <v>130229292</v>
       </c>
       <c r="B3" t="n">
-        <v>97578</v>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +912,7 @@
         <v>130229175</v>
       </c>
       <c r="B4" t="n">
-        <v>91534</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,6 +1013,132 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130229034</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dimlingbacken, Dimlingbacken, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>282970</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6528781</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34080-2023 artfynd.xlsx
+++ b/artfynd/A 34080-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229292</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229175</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,8 +1159,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>